--- a/doc/print_settings/strength/infill_desc_calculator.xlsx
+++ b/doc/print_settings/strength/infill_desc_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Repos\OrcaSlicer\doc\print_settings\strength\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0BE5E4-0477-4562-81CA-E1D6663BBB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD05B65A-2F9C-49E4-AE7D-66DB48051586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{F7BCEEB8-8D62-4686-9FA1-C052039D2FF8}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Grid</t>
   </si>
   <si>
-    <t>2D Lattice</t>
-  </si>
-  <si>
     <t>Line</t>
   </si>
   <si>
@@ -246,9 +243,6 @@
     <t>Material/Time</t>
   </si>
   <si>
-    <t>2D Honeycomb</t>
-  </si>
-  <si>
     <t>Ultra-Low</t>
   </si>
   <si>
@@ -350,9 +344,6 @@
     <t>ipGrid</t>
   </si>
   <si>
-    <t>ip2DLattice</t>
-  </si>
-  <si>
     <t>ipLine</t>
   </si>
   <si>
@@ -386,9 +377,6 @@
     <t>ipAlignedRectilinear</t>
   </si>
   <si>
-    <t>ip2DHoneycomb</t>
-  </si>
-  <si>
     <t>ip3DHoneycomb</t>
   </si>
   <si>
@@ -443,9 +431,6 @@
     <t>grid</t>
   </si>
   <si>
-    <t>2dlattice</t>
-  </si>
-  <si>
     <t>line</t>
   </si>
   <si>
@@ -473,9 +458,6 @@
     <t>alignedrectilinear</t>
   </si>
   <si>
-    <t>2dhoneycomb</t>
-  </si>
-  <si>
     <t>3dhoneycomb</t>
   </si>
   <si>
@@ -548,9 +530,6 @@
     <t>Basic</t>
   </si>
   <si>
-    <t>2D</t>
-  </si>
-  <si>
     <t>TPMS</t>
   </si>
   <si>
@@ -618,6 +597,27 @@
   </si>
   <si>
     <t>Applies to</t>
+  </si>
+  <si>
+    <t>ipLateralLattice</t>
+  </si>
+  <si>
+    <t>ipLateralHoneycomb</t>
+  </si>
+  <si>
+    <t>Lateral Honeycomb</t>
+  </si>
+  <si>
+    <t>Lateral Lattice</t>
+  </si>
+  <si>
+    <t>Lateral</t>
+  </si>
+  <si>
+    <t>lateral-honeycomb</t>
+  </si>
+  <si>
+    <t>lateral-lattice</t>
   </si>
 </sst>
 </file>
@@ -670,7 +670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -684,8 +684,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,7 +691,22 @@
   </cellStyles>
   <dxfs count="28">
     <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -734,22 +747,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -768,6 +765,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <font>
@@ -980,23 +978,23 @@
     <tableColumn id="13" xr3:uid="{F80BCD33-B1E3-433F-AF6D-F982D670E727}" name="Material/Time" dataDxfId="10" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Infill[[#This Row],[g/t prom]],Rating[Max %],Rating[Name],,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44AE3D7E-C8D1-4165-B6BD-E525E4F90672}" name="nameMD" dataDxfId="3" dataCellStyle="Porcentaje">
+    <tableColumn id="19" xr3:uid="{44AE3D7E-C8D1-4165-B6BD-E525E4F90672}" name="nameMD" dataDxfId="9" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>SUBSTITUTE(LOWER(Infill[[#This Row],[name]])," ","-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{9C188045-ECA6-4734-BC61-4D569A3256F0}" name="SVG" dataDxfId="9" dataCellStyle="Porcentaje"/>
-    <tableColumn id="34" xr3:uid="{45B271D4-A035-4A01-B06E-E3B623BB568E}" name="SVG Link" dataDxfId="8">
+    <tableColumn id="33" xr3:uid="{9C188045-ECA6-4734-BC61-4D569A3256F0}" name="SVG" dataDxfId="8" dataCellStyle="Porcentaje"/>
+    <tableColumn id="34" xr3:uid="{45B271D4-A035-4A01-B06E-E3B623BB568E}" name="SVG Link" dataDxfId="7">
       <calculatedColumnFormula>"!["&amp;Infill[[#This Row],[SVG]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/"&amp;Infill[[#This Row],[SVG]]&amp;".svg?raw=true)"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{75AA760A-15C0-4692-B168-BF74BE6D50F6}" name="Pattern" dataDxfId="1" dataCellStyle="Porcentaje">
+    <tableColumn id="21" xr3:uid="{75AA760A-15C0-4692-B168-BF74BE6D50F6}" name="Pattern" dataDxfId="6" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{D12C345A-0415-4208-969C-FE76BD14B76A}" name="Applies to" dataDxfId="2" dataCellStyle="Porcentaje">
+    <tableColumn id="31" xr3:uid="{D12C345A-0415-4208-969C-FE76BD14B76A}" name="Applies to" dataDxfId="5" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{AE92B56B-1C4F-4A43-BC18-AFFF1480255E}" name="MD" dataDxfId="0" dataCellStyle="Porcentaje">
+    <tableColumn id="14" xr3:uid="{AE92B56B-1C4F-4A43-BC18-AFFF1480255E}" name="MD" dataDxfId="4" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -1010,13 +1008,13 @@
 ![infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;".png?raw=true)
 ","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{B5B3DE03-E8E0-4448-BA81-E5B849AC0415}" name="s_keys_map" dataDxfId="7" dataCellStyle="Porcentaje">
+    <tableColumn id="26" xr3:uid="{B5B3DE03-E8E0-4448-BA81-E5B849AC0415}" name="s_keys_map" dataDxfId="3" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]])," { """&amp;Infill[[#This Row],[infill]]&amp;""", "&amp;Infill[[#This Row],[ip]]&amp;" },","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{DF1D46A6-663C-4993-9678-9483ECBDC09A}" name="Enum Pattern" dataDxfId="6" dataCellStyle="Porcentaje">
+    <tableColumn id="30" xr3:uid="{DF1D46A6-663C-4993-9678-9483ECBDC09A}" name="Enum Pattern" dataDxfId="2" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_values.push_back("""&amp;Infill[[#This Row],[infill]]&amp;""");","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{A375012B-C9F3-4FDF-8EA3-593D97EDEB2B}" name="Enum Pattern Names" dataDxfId="5" dataCellStyle="Porcentaje">
+    <tableColumn id="29" xr3:uid="{A375012B-C9F3-4FDF-8EA3-593D97EDEB2B}" name="Enum Pattern Names" dataDxfId="1" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1040,7 +1038,7 @@
   <autoFilter ref="A16:C25" xr:uid="{8371D3BF-96D7-48EB-82A0-8021F9AA952E}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1D00CA6A-CEDD-45A1-8BA8-6DB7769D516C}" name="N"/>
-    <tableColumn id="2" xr3:uid="{3AC9B406-037B-4FD3-80D6-86F4D94EDB36}" name="Max %" dataDxfId="4" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{3AC9B406-037B-4FD3-80D6-86F4D94EDB36}" name="Max %" dataDxfId="0" dataCellStyle="Porcentaje"/>
     <tableColumn id="3" xr3:uid="{18E14714-6899-4575-90B8-4F97863AF141}" name="Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1409,120 +1407,120 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="N1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s">
+        <v>75</v>
+      </c>
+      <c r="W1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH1" t="s">
         <v>185</v>
       </c>
-      <c r="I1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="AI1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL1" t="s">
         <v>158</v>
-      </c>
-      <c r="M1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" t="s">
-        <v>77</v>
-      </c>
-      <c r="W1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1537,19 +1535,19 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -1566,7 +1564,7 @@
         <v>Normal</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S2">
         <v>7</v>
@@ -1676,10 +1674,10 @@
     </row>
     <row r="3" spans="1:38" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1694,19 +1692,19 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -1723,7 +1721,7 @@
         <v>Normal</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S3">
         <v>9</v>
@@ -1833,7 +1831,7 @@
     </row>
     <row r="4" spans="1:38" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2">
         <v>0.15</v>
@@ -1857,13 +1855,13 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -1880,7 +1878,7 @@
         <v>Low</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -1993,10 +1991,10 @@
     </row>
     <row r="5" spans="1:38" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2011,19 +2009,19 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -2040,7 +2038,7 @@
         <v>Normal</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S5">
         <v>8</v>
@@ -2152,10 +2150,10 @@
     </row>
     <row r="6" spans="1:38" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -2170,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -2199,7 +2197,7 @@
         <v>Low</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -2306,10 +2304,10 @@
     </row>
     <row r="7" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -2324,19 +2322,19 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J7" t="s">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N7">
         <v>4</v>
@@ -2353,7 +2351,7 @@
         <v>Low</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -2460,7 +2458,7 @@
     </row>
     <row r="8" spans="1:38" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
@@ -2478,19 +2476,19 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -2507,7 +2505,7 @@
         <v>Normal-Low</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S8">
         <v>15</v>
@@ -2614,7 +2612,7 @@
     </row>
     <row r="9" spans="1:38" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -2632,19 +2630,19 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" t="s">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N9">
         <v>2</v>
@@ -2661,7 +2659,7 @@
         <v>Low</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S9">
         <v>7</v>
@@ -2768,10 +2766,10 @@
     </row>
     <row r="10" spans="1:38" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -2789,16 +2787,16 @@
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N10">
         <v>6</v>
@@ -2815,7 +2813,7 @@
         <v>High</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S10">
         <v>8</v>
@@ -2922,10 +2920,10 @@
     </row>
     <row r="11" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -2940,19 +2938,19 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -2969,7 +2967,7 @@
         <v>Normal</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -3076,10 +3074,10 @@
     </row>
     <row r="12" spans="1:38" ht="105" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -3094,19 +3092,19 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N12">
         <v>6</v>
@@ -3123,7 +3121,7 @@
         <v>Normal-High</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S12">
         <v>7</v>
@@ -3242,19 +3240,19 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -3271,7 +3269,7 @@
         <v>High</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S13">
         <v>7</v>
@@ -3390,19 +3388,19 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -3419,7 +3417,7 @@
         <v>Normal-High</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="S14">
         <v>5</v>
@@ -3538,19 +3536,19 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L15" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -3567,7 +3565,7 @@
         <v>High</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -3674,13 +3672,13 @@
     </row>
     <row r="16" spans="1:38" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>14</v>
@@ -3695,19 +3693,19 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="K16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L16" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -3724,7 +3722,7 @@
         <v>Low</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S16">
         <v>2</v>
@@ -3837,7 +3835,7 @@
         <v>0.15</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17">
         <v>15</v>
@@ -3852,19 +3850,19 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L17" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N17">
         <v>2</v>
@@ -3881,7 +3879,7 @@
         <v>Low</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S17">
         <v>1</v>
@@ -3994,7 +3992,7 @@
         <v>0.4</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>16</v>
@@ -4009,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N18">
         <v>6</v>
@@ -4038,7 +4036,7 @@
         <v>High</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S18">
         <v>17</v>
@@ -4151,7 +4149,7 @@
         <v>0.75</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19">
         <v>17</v>
@@ -4166,19 +4164,19 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -4195,7 +4193,7 @@
         <v>Normal-High</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S19">
         <v>12</v>
@@ -4308,7 +4306,7 @@
         <v>0.92500000000000004</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>18</v>
@@ -4323,19 +4321,19 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="J20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K20" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N20">
         <v>3</v>
@@ -4352,7 +4350,7 @@
         <v>Normal-Low</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S20">
         <v>8</v>
@@ -4397,19 +4395,19 @@
       </c>
       <c r="AD20" s="2" t="str">
         <f>SUBSTITUTE(LOWER(Infill[[#This Row],[name]])," ","-")</f>
-        <v>2d-honeycomb</v>
+        <v>lateral-honeycomb</v>
       </c>
       <c r="AE20" t="str">
         <f>"param_"&amp;Infill[[#This Row],[infill]]</f>
-        <v>param_2dhoneycomb</v>
+        <v>param_lateral-honeycomb</v>
       </c>
       <c r="AF20" t="str">
         <f>"!["&amp;Infill[[#This Row],[SVG]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/"&amp;Infill[[#This Row],[SVG]]&amp;".svg?raw=true)"</f>
-        <v>![param_2dhoneycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_2dhoneycomb.svg?raw=true)</v>
+        <v>![param_lateral-honeycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_lateral-honeycomb.svg?raw=true)</v>
       </c>
       <c r="AG20" s="2" t="str">
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
-        <v>[2D Honeycomb](#2d-honeycomb)</v>
+        <v>[Lateral Honeycomb](#lateral-honeycomb)</v>
       </c>
       <c r="AH20" s="5" t="str">
         <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
@@ -4431,7 +4429,7 @@
 "&amp;Infill[[#This Row],[Applies to]]&amp;"
 ![infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;".png?raw=true)
 ","")</f>
-        <v xml:space="preserve">## 2D Honeycomb
+        <v xml:space="preserve">## Lateral Honeycomb
 Vertical Honeycomb pattern. Acceptable torsional stiffness. Developed for low densities structures like wings. Improve over [2D Lattice](#2d-lattice) offers same performance with lower densities.This infill includes a Overhang angle parameter to improve the point of contact between layers and reduce the risk of delamination.
 - **Horizontal Strength (X-Y):** Normal-Low
 - **Vertical Strength (Z):** Normal-Low
@@ -4441,20 +4439,20 @@
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
   - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-![infill-top-2d-honeycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-2d-honeycomb.png?raw=true)
+![infill-top-lateral-honeycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-lateral-honeycomb.png?raw=true)
 </v>
       </c>
       <c r="AJ20" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]])," { """&amp;Infill[[#This Row],[infill]]&amp;""", "&amp;Infill[[#This Row],[ip]]&amp;" },","")</f>
-        <v xml:space="preserve"> { "2dhoneycomb", ip2DHoneycomb },</v>
+        <v xml:space="preserve"> { "lateral-honeycomb", ipLateralHoneycomb },</v>
       </c>
       <c r="AK20" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_values.push_back("""&amp;Infill[[#This Row],[infill]]&amp;""");","")</f>
-        <v>def-&gt;enum_values.push_back("2dhoneycomb");</v>
+        <v>def-&gt;enum_values.push_back("lateral-honeycomb");</v>
       </c>
       <c r="AL20" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
-        <v>def-&gt;enum_labels.push_back(L("2D Honeycomb"));</v>
+        <v>def-&gt;enum_labels.push_back(L("Lateral Honeycomb"));</v>
       </c>
     </row>
     <row r="21" spans="1:38" ht="120" x14ac:dyDescent="0.25">
@@ -4465,7 +4463,7 @@
         <v>1.075</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21">
         <v>19</v>
@@ -4480,19 +4478,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="J21" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="K21" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N21">
         <v>3</v>
@@ -4509,7 +4507,7 @@
         <v>Low</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -4554,19 +4552,19 @@
       </c>
       <c r="AD21" s="2" t="str">
         <f>SUBSTITUTE(LOWER(Infill[[#This Row],[name]])," ","-")</f>
-        <v>2d-lattice</v>
+        <v>lateral-lattice</v>
       </c>
       <c r="AE21" t="str">
         <f>"param_"&amp;Infill[[#This Row],[infill]]</f>
-        <v>param_2dlattice</v>
+        <v>param_lateral-lattice</v>
       </c>
       <c r="AF21" t="str">
         <f>"!["&amp;Infill[[#This Row],[SVG]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/"&amp;Infill[[#This Row],[SVG]]&amp;".svg?raw=true)"</f>
-        <v>![param_2dlattice](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_2dlattice.svg?raw=true)</v>
+        <v>![param_lateral-lattice](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_lateral-lattice.svg?raw=true)</v>
       </c>
       <c r="AG21" s="2" t="str">
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
-        <v>[2D Lattice](#2d-lattice)</v>
+        <v>[Lateral Lattice](#lateral-lattice)</v>
       </c>
       <c r="AH21" s="5" t="str">
         <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
@@ -4588,7 +4586,7 @@
 "&amp;Infill[[#This Row],[Applies to]]&amp;"
 ![infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;".png?raw=true)
 ","")</f>
-        <v xml:space="preserve">## 2D Lattice
+        <v xml:space="preserve">## Lateral Lattice
 Low-strength pattern with good flexibility. You can adjust **Angle 1** and **Angle 2** to optimize the infill for your specific model. Each angle adjusts the plane of each layer generated by the pattern. 0° is vertical.
 - **Horizontal Strength (X-Y):** Normal-Low
 - **Vertical Strength (Z):** Low
@@ -4598,20 +4596,20 @@
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
   - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-![infill-top-2d-lattice](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-2d-lattice.png?raw=true)
+![infill-top-lateral-lattice](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-lateral-lattice.png?raw=true)
 </v>
       </c>
       <c r="AJ21" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]])," { """&amp;Infill[[#This Row],[infill]]&amp;""", "&amp;Infill[[#This Row],[ip]]&amp;" },","")</f>
-        <v xml:space="preserve"> { "2dlattice", ip2DLattice },</v>
+        <v xml:space="preserve"> { "lateral-lattice", ipLateralLattice },</v>
       </c>
       <c r="AK21" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_values.push_back("""&amp;Infill[[#This Row],[infill]]&amp;""");","")</f>
-        <v>def-&gt;enum_values.push_back("2dlattice");</v>
+        <v>def-&gt;enum_values.push_back("lateral-lattice");</v>
       </c>
       <c r="AL21" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
-        <v>def-&gt;enum_labels.push_back(L("2D Lattice"));</v>
+        <v>def-&gt;enum_labels.push_back(L("Lateral Lattice"));</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="105" x14ac:dyDescent="0.25">
@@ -4622,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22">
         <v>20</v>
@@ -4637,19 +4635,19 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L22" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -4666,7 +4664,7 @@
         <v>Normal-High</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -4780,7 +4778,7 @@
         <v>1.6</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>21</v>
@@ -4795,19 +4793,19 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -4824,7 +4822,7 @@
         <v>High</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S23">
         <v>11</v>
@@ -4937,7 +4935,7 @@
         <v>1.85</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E24">
         <v>22</v>
@@ -4952,36 +4950,36 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J24" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K24" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="N24" s="9">
+        <v>177</v>
+      </c>
+      <c r="N24">
         <v>5</v>
       </c>
-      <c r="O24" s="9" t="str">
+      <c r="O24" t="str">
         <f>_xlfn.XLOOKUP(Infill[[#This Row],[XY-N]],Rating[N],Rating[Name])</f>
         <v>Normal-High</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24">
         <v>5</v>
       </c>
-      <c r="Q24" s="9" t="str">
+      <c r="Q24" t="str">
         <f>_xlfn.XLOOKUP(Infill[[#This Row],[Z-N]],Rating[N],Rating[Name])</f>
         <v>Normal-High</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S24">
         <v>12</v>
@@ -4992,7 +4990,7 @@
       <c r="U24">
         <v>149.02000000000001</v>
       </c>
-      <c r="V24" s="10">
+      <c r="V24" s="2">
         <f>Infill[[#This Row],[g]]/(997.25*0.15)</f>
         <v>0.99620623380964324</v>
       </c>
@@ -5000,11 +4998,11 @@
         <f>_xlfn.XLOOKUP(Infill[[#This Row],[% Effective]],Rating[Max %],Rating[Name],,1)</f>
         <v>Normal</v>
       </c>
-      <c r="X24" s="9">
+      <c r="X24">
         <f>Infill[[#This Row],[hs]]*60+Infill[[#This Row],[min]]</f>
         <v>769</v>
       </c>
-      <c r="Y24" s="10">
+      <c r="Y24" s="2">
         <f>Infill[[#This Row],[Total Time]]/AVERAGEIFS(Infill[Total Time],Infill[Material Usage],"Normal")</f>
         <v>1.4259946055293324</v>
       </c>
@@ -5016,7 +5014,7 @@
         <f>Infill[[#This Row],[g]]/Infill[[#This Row],[Total Time]]</f>
         <v>0.1937841352405722</v>
       </c>
-      <c r="AB24" s="10">
+      <c r="AB24" s="2">
         <f>Infill[[#This Row],[g/t]]/AVERAGEIFS(Infill[g/t],Infill[Material Usage],"Normal")</f>
         <v>0.68144702891351949</v>
       </c>
@@ -5024,7 +5022,7 @@
         <f>_xlfn.XLOOKUP(Infill[[#This Row],[g/t prom]],Rating[Max %],Rating[Name],,1)</f>
         <v>Low</v>
       </c>
-      <c r="AD24" s="10" t="str">
+      <c r="AD24" s="2" t="str">
         <f>SUBSTITUTE(LOWER(Infill[[#This Row],[name]])," ","-")</f>
         <v>tpms-fk</v>
       </c>
@@ -5032,11 +5030,11 @@
         <f>"param_"&amp;Infill[[#This Row],[infill]]</f>
         <v>param_tpmsfk</v>
       </c>
-      <c r="AF24" s="9" t="str">
+      <c r="AF24" t="str">
         <f>"!["&amp;Infill[[#This Row],[SVG]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/"&amp;Infill[[#This Row],[SVG]]&amp;".svg?raw=true)"</f>
         <v>![param_tpmsfk](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_tpmsfk.svg?raw=true)</v>
       </c>
-      <c r="AG24" s="10" t="str">
+      <c r="AG24" s="2" t="str">
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[TPMS-FK](#tpms-fk)</v>
       </c>
@@ -5047,7 +5045,7 @@
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI24" s="10" t="str">
+      <c r="AI24" s="2" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5094,7 +5092,7 @@
         <v>9.99</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E25">
         <v>23</v>
@@ -5109,19 +5107,19 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J25" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K25" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N25">
         <v>6</v>
@@ -5138,7 +5136,7 @@
         <v>High</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -5260,16 +5258,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="5">
         <v>2</v>
@@ -5286,7 +5284,7 @@
         <v>Normal</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S26">
         <v>8</v>
@@ -5411,19 +5409,19 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L27" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -5440,7 +5438,7 @@
         <v>Normal</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S27">
         <v>13</v>
@@ -5564,19 +5562,19 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K28" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N28">
         <v>2</v>
@@ -5593,7 +5591,7 @@
         <v>Normal</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -5716,19 +5714,19 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J29" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L29" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -5745,7 +5743,7 @@
         <v>Normal</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S29">
         <v>9</v>
@@ -5868,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M30" s="8"/>
       <c r="O30" t="e">
@@ -5973,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M31" s="8"/>
       <c r="O31" t="e">
@@ -6078,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M32" s="8"/>
       <c r="O32" t="e">

--- a/doc/print_settings/strength/infill_desc_calculator.xlsx
+++ b/doc/print_settings/strength/infill_desc_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Repos\OrcaSlicer\doc\print_settings\strength\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD05B65A-2F9C-49E4-AE7D-66DB48051586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F288D4-B9A1-47D5-A3F9-DAAC4F36020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{F7BCEEB8-8D62-4686-9FA1-C052039D2FF8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="194">
   <si>
     <t>Concentric</t>
   </si>
@@ -313,9 +313,6 @@
     <t>Mathematical, isotropic surface providing equal strength in all directions. Excellent for strong, flexible prints and resin filling due to its interconnected structure. This pattern may require more time to slice because of all the points needed to generate each curve. If your model has complex geometry, consider using a simpler infill pattern like [TPMS-D](#tpms-d) or [Cross Hatch](#cross-hatch).</t>
   </si>
   <si>
-    <t>Vertical Honeycomb pattern. Acceptable torsional stiffness. Developed for low densities structures like wings. Improve over [2D Lattice](#2d-lattice) offers same performance with lower densities.This infill includes a Overhang angle parameter to improve the point of contact between layers and reduce the risk of delamination.</t>
-  </si>
-  <si>
     <t>This infill tries to generate a printable honeycomb structure by printing squares and octagons maintaining a vertical angle high enough to maintain contact with the previous layer.</t>
   </si>
   <si>
@@ -618,6 +615,12 @@
   </si>
   <si>
     <t>lateral-lattice</t>
+  </si>
+  <si>
+    <t>Vertical Honeycomb pattern. Acceptable torsional stiffness. Developed for low densities structures like wings. Improve over [Lateral Lattice](#lateral-lattice) offers same performance with lower densities.This infill includes a Overhang angle parameter to improve the point of contact between layers and reduce the risk of delamination.</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -670,7 +673,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -684,14 +687,29 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="35">
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -704,6 +722,18 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -941,60 +971,59 @@
     <tableColumn id="32" xr3:uid="{A02F4DC8-DB89-4104-8C6F-95945DF0135D}" name="Group"/>
     <tableColumn id="24" xr3:uid="{6521A458-B14C-427C-865F-121955BAA369}" name="ip"/>
     <tableColumn id="25" xr3:uid="{956F45F2-2962-4E6E-81C2-F10A02B550B8}" name="infill"/>
-    <tableColumn id="18" xr3:uid="{0AF02225-407A-4366-B524-2DC6A8FF6278}" name="Desc" dataDxfId="27" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{EDA17F6B-F438-45F7-B1D4-D47E28684329}" name="XY-N" dataDxfId="26"/>
-    <tableColumn id="17" xr3:uid="{94F205F5-D170-40A1-8C5F-879C636804AA}" name="X-Y Strength" dataDxfId="25">
+    <tableColumn id="18" xr3:uid="{0AF02225-407A-4366-B524-2DC6A8FF6278}" name="Desc" dataDxfId="34" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{EDA17F6B-F438-45F7-B1D4-D47E28684329}" name="XY-N" dataDxfId="33"/>
+    <tableColumn id="17" xr3:uid="{94F205F5-D170-40A1-8C5F-879C636804AA}" name="X-Y Strength" dataDxfId="32">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Infill[[#This Row],[XY-N]],Rating[N],Rating[Name])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{E9317962-9E1D-4D5B-9028-66E03DB4FC89}" name="Z-N" dataDxfId="24"/>
-    <tableColumn id="16" xr3:uid="{D6A80A00-4E52-418C-9F58-C091734E73D4}" name="Z Strength" dataDxfId="23">
+    <tableColumn id="20" xr3:uid="{E9317962-9E1D-4D5B-9028-66E03DB4FC89}" name="Z-N" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{D6A80A00-4E52-418C-9F58-C091734E73D4}" name="Z Strength" dataDxfId="30">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Infill[[#This Row],[Z-N]],Rating[N],Rating[Name])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{A5F7A5DA-C5EE-4BAA-9BF1-1AF83AB88E06}" name="DensityCalc" dataDxfId="22" dataCellStyle="Porcentaje"/>
+    <tableColumn id="15" xr3:uid="{A5F7A5DA-C5EE-4BAA-9BF1-1AF83AB88E06}" name="DensityCalc" dataDxfId="29" dataCellStyle="Porcentaje"/>
     <tableColumn id="5" xr3:uid="{CC2FB322-5D42-4375-BC4F-16927902366E}" name="hs"/>
     <tableColumn id="2" xr3:uid="{0B06FA91-5EDF-466A-8753-FFCA36B0EFB0}" name="min"/>
-    <tableColumn id="3" xr3:uid="{E842218B-6949-43A1-A35A-6C35A7D812BB}" name="g" totalsRowFunction="average" totalsRowDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{55891199-0C82-4B3C-B416-4BE5775CD688}" name="% Effective" totalsRowFunction="average" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Porcentaje">
+    <tableColumn id="3" xr3:uid="{E842218B-6949-43A1-A35A-6C35A7D812BB}" name="g" totalsRowFunction="average" totalsRowDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{55891199-0C82-4B3C-B416-4BE5775CD688}" name="% Effective" totalsRowFunction="average" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>Infill[[#This Row],[g]]/(997.25*0.15)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{32CE485A-842B-45B3-8F5D-B93DF0C49C8F}" name="Material Usage" dataDxfId="18" dataCellStyle="Porcentaje">
+    <tableColumn id="11" xr3:uid="{32CE485A-842B-45B3-8F5D-B93DF0C49C8F}" name="Material Usage" dataDxfId="25" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Infill[[#This Row],[% Effective]],Rating[Max %],Rating[Name],,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C7DC0832-87AA-48F2-8845-AAE7F7254500}" name="Total Time" totalsRowFunction="average" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="6" xr3:uid="{C7DC0832-87AA-48F2-8845-AAE7F7254500}" name="Total Time" totalsRowFunction="average" dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>Infill[[#This Row],[hs]]*60+Infill[[#This Row],[min]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{252F6390-A339-497F-955E-B7D85B035B56}" name="t prom" dataDxfId="15" dataCellStyle="Porcentaje">
+    <tableColumn id="8" xr3:uid="{252F6390-A339-497F-955E-B7D85B035B56}" name="t prom" dataDxfId="22" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>Infill[[#This Row],[Total Time]]/AVERAGEIFS(Infill[Total Time],Infill[Material Usage],"Normal")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0224A6DD-647D-41E2-B74E-256AAEBCEDB8}" name="Print Time" dataDxfId="14" dataCellStyle="Porcentaje">
+    <tableColumn id="12" xr3:uid="{0224A6DD-647D-41E2-B74E-256AAEBCEDB8}" name="Print Time" dataDxfId="21" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Infill[[#This Row],[t prom]],Rating[Max %],Rating[Name],,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3A33F243-4754-4015-A3B1-EEAA7B810730}" name="g/t" totalsRowFunction="average" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Porcentaje">
+    <tableColumn id="7" xr3:uid="{3A33F243-4754-4015-A3B1-EEAA7B810730}" name="g/t" totalsRowFunction="average" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>Infill[[#This Row],[g]]/Infill[[#This Row],[Total Time]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{81F5FB07-EC80-4D98-B9AE-8EF8E1629F1A}" name="g/t prom" dataDxfId="11" dataCellStyle="Porcentaje">
+    <tableColumn id="10" xr3:uid="{81F5FB07-EC80-4D98-B9AE-8EF8E1629F1A}" name="g/t prom" dataDxfId="18" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>Infill[[#This Row],[g/t]]/AVERAGEIFS(Infill[g/t],Infill[Material Usage],"Normal")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F80BCD33-B1E3-433F-AF6D-F982D670E727}" name="Material/Time" dataDxfId="10" dataCellStyle="Porcentaje">
+    <tableColumn id="13" xr3:uid="{F80BCD33-B1E3-433F-AF6D-F982D670E727}" name="Material/Time" dataDxfId="17" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Infill[[#This Row],[g/t prom]],Rating[Max %],Rating[Name],,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44AE3D7E-C8D1-4165-B6BD-E525E4F90672}" name="nameMD" dataDxfId="9" dataCellStyle="Porcentaje">
+    <tableColumn id="19" xr3:uid="{44AE3D7E-C8D1-4165-B6BD-E525E4F90672}" name="nameMD" dataDxfId="16" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>SUBSTITUTE(LOWER(Infill[[#This Row],[name]])," ","-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{9C188045-ECA6-4734-BC61-4D569A3256F0}" name="SVG" dataDxfId="8" dataCellStyle="Porcentaje"/>
-    <tableColumn id="34" xr3:uid="{45B271D4-A035-4A01-B06E-E3B623BB568E}" name="SVG Link" dataDxfId="7">
+    <tableColumn id="33" xr3:uid="{9C188045-ECA6-4734-BC61-4D569A3256F0}" name="SVG" dataDxfId="15" dataCellStyle="Porcentaje"/>
+    <tableColumn id="34" xr3:uid="{45B271D4-A035-4A01-B06E-E3B623BB568E}" name="SVG Link" dataDxfId="14">
       <calculatedColumnFormula>"!["&amp;Infill[[#This Row],[SVG]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/"&amp;Infill[[#This Row],[SVG]]&amp;".svg?raw=true)"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{75AA760A-15C0-4692-B168-BF74BE6D50F6}" name="Pattern" dataDxfId="6" dataCellStyle="Porcentaje">
+    <tableColumn id="21" xr3:uid="{75AA760A-15C0-4692-B168-BF74BE6D50F6}" name="Pattern" dataDxfId="13" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{D12C345A-0415-4208-969C-FE76BD14B76A}" name="Applies to" dataDxfId="5" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+    <tableColumn id="31" xr3:uid="{D12C345A-0415-4208-969C-FE76BD14B76A}" name="Applies to" dataDxfId="0" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{AE92B56B-1C4F-4A43-BC18-AFFF1480255E}" name="MD" dataDxfId="4" dataCellStyle="Porcentaje">
+    <tableColumn id="14" xr3:uid="{AE92B56B-1C4F-4A43-BC18-AFFF1480255E}" name="MD" dataDxfId="1" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -1008,13 +1037,13 @@
 ![infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;".png?raw=true)
 ","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{B5B3DE03-E8E0-4448-BA81-E5B849AC0415}" name="s_keys_map" dataDxfId="3" dataCellStyle="Porcentaje">
+    <tableColumn id="26" xr3:uid="{B5B3DE03-E8E0-4448-BA81-E5B849AC0415}" name="s_keys_map" dataDxfId="12" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]])," { """&amp;Infill[[#This Row],[infill]]&amp;""", "&amp;Infill[[#This Row],[ip]]&amp;" },","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{DF1D46A6-663C-4993-9678-9483ECBDC09A}" name="Enum Pattern" dataDxfId="2" dataCellStyle="Porcentaje">
+    <tableColumn id="30" xr3:uid="{DF1D46A6-663C-4993-9678-9483ECBDC09A}" name="Enum Pattern" dataDxfId="11" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_values.push_back("""&amp;Infill[[#This Row],[infill]]&amp;""");","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{A375012B-C9F3-4FDF-8EA3-593D97EDEB2B}" name="Enum Pattern Names" dataDxfId="1" dataCellStyle="Porcentaje">
+    <tableColumn id="29" xr3:uid="{A375012B-C9F3-4FDF-8EA3-593D97EDEB2B}" name="Enum Pattern Names" dataDxfId="10" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1038,8 +1067,38 @@
   <autoFilter ref="A16:C25" xr:uid="{8371D3BF-96D7-48EB-82A0-8021F9AA952E}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1D00CA6A-CEDD-45A1-8BA8-6DB7769D516C}" name="N"/>
-    <tableColumn id="2" xr3:uid="{3AC9B406-037B-4FD3-80D6-86F4D94EDB36}" name="Max %" dataDxfId="0" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{3AC9B406-037B-4FD3-80D6-86F4D94EDB36}" name="Max %" dataDxfId="9" dataCellStyle="Porcentaje"/>
     <tableColumn id="3" xr3:uid="{18E14714-6899-4575-90B8-4F97863AF141}" name="Name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F85400E8-93F1-42C5-93F9-13851BAE5398}" name="Tabla4" displayName="Tabla4" ref="AN1:AT32" totalsRowShown="0">
+  <autoFilter ref="AN1:AT32" xr:uid="{F85400E8-93F1-42C5-93F9-13851BAE5398}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{184C8A2D-5FE4-4972-8525-02DD0ED763F3}" name="-" dataDxfId="8">
+      <calculatedColumnFormula>Infill[[#This Row],[SVG Link]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{14A2CB57-4B88-4948-ABB5-B4E1F3AB50EF}" name="Pattern" dataDxfId="7">
+      <calculatedColumnFormula>Infill[[#This Row],[Pattern]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{7FB40202-1341-4B88-81D2-89C268F45D4D}" name="Applies to" dataDxfId="6">
+      <calculatedColumnFormula>Infill[[#This Row],[Applies to]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{F83791FA-52BD-4574-8359-2DC84F1575E3}" name="X-Y Strength" dataDxfId="5">
+      <calculatedColumnFormula>Infill[[#This Row],[X-Y Strength]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{A30810A1-1E95-4BAA-97B8-93C571CB8CF0}" name="Z Strength" dataDxfId="4">
+      <calculatedColumnFormula>Infill[[#This Row],[Z Strength]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{630ACA64-21F3-4422-B317-D820E5C1F820}" name="Material Usage" dataDxfId="3">
+      <calculatedColumnFormula>Infill[[#This Row],[Material/Time]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{5F0A6FFD-7381-42EE-8794-FC0492BBA85C}" name="Print Time" dataDxfId="2">
+      <calculatedColumnFormula>Infill[[#This Row],[Print Time]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1362,50 +1421,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F62B1C-B5D3-443B-88E3-A492D48347EC}">
-  <dimension ref="A1:AL32"/>
+  <dimension ref="A1:AT32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.85546875" customWidth="1"/>
-    <col min="9" max="9" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5703125" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="56.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="59.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="139.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="52.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="50.42578125" customWidth="1"/>
-    <col min="35" max="35" width="54.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="59.5703125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="63.5703125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="94.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="226.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="56.85546875" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="139.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="226.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -1413,28 +1479,28 @@
         <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" t="s">
         <v>155</v>
       </c>
-      <c r="G1" t="s">
-        <v>156</v>
-      </c>
       <c r="H1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M1" t="s">
         <v>40</v>
@@ -1488,34 +1554,55 @@
         <v>67</v>
       </c>
       <c r="AD1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF1" t="s">
         <v>166</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>167</v>
       </c>
       <c r="AG1" t="s">
         <v>86</v>
       </c>
       <c r="AH1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AI1" t="s">
         <v>81</v>
       </c>
       <c r="AJ1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AK1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL1" t="s">
         <v>157</v>
       </c>
-      <c r="AL1" t="s">
-        <v>158</v>
+      <c r="AN1" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="314.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1535,19 +1622,19 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -1623,16 +1710,14 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Monotonic](#monotonic)</v>
       </c>
-      <c r="AH2" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH2" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
-      <c r="AI2" s="2" t="str">
+      <c r="AI2" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -1671,8 +1756,37 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Monotonic"));</v>
       </c>
+      <c r="AN2" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_monotonic](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_monotonic.svg?raw=true)</v>
+      </c>
+      <c r="AO2" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Monotonic](#monotonic)</v>
+      </c>
+      <c r="AP2" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**</v>
+      </c>
+      <c r="AQ2" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AR2" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS2" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT2" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="3" spans="1:38" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" ht="255" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1692,19 +1806,19 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -1780,16 +1894,14 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Monotonic line](#monotonic-line)</v>
       </c>
-      <c r="AH3" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH3" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
-      <c r="AI3" s="2" t="str">
+      <c r="AI3" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -1828,8 +1940,37 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Monotonic line"));</v>
       </c>
+      <c r="AN3" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_monotonicline](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_monotonicline.svg?raw=true)</v>
+      </c>
+      <c r="AO3" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Monotonic line](#monotonic-line)</v>
+      </c>
+      <c r="AP3" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**</v>
+      </c>
+      <c r="AQ3" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AR3" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS3" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT3" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal</v>
+      </c>
     </row>
-    <row r="4" spans="1:38" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="270" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1855,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>88</v>
@@ -1937,17 +2078,15 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Rectilinear](#rectilinear)</v>
       </c>
-      <c r="AH4" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH4" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**</v>
       </c>
-      <c r="AI4" s="2" t="str">
+      <c r="AI4" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -1969,8 +2108,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**
 ![infill-top-rectilinear](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-rectilinear.png?raw=true)
@@ -1988,8 +2126,38 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Rectilinear"));</v>
       </c>
+      <c r="AN4" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_rectilinear](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_rectilinear.svg?raw=true)</v>
+      </c>
+      <c r="AO4" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Rectilinear](#rectilinear)</v>
+      </c>
+      <c r="AP4" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**
+  - **[Ironing](quality_settings_ironing)**</v>
+      </c>
+      <c r="AQ4" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AR4" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS4" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT4" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="5" spans="1:38" ht="150" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="270" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2015,10 +2183,10 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>62</v>
@@ -2097,16 +2265,14 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Aligned Rectilinear](#aligned-rectilinear)</v>
       </c>
-      <c r="AH5" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH5" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
-      <c r="AI5" s="2" t="str">
+      <c r="AI5" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -2129,8 +2295,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-aligned-rectilinear](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-aligned-rectilinear.png?raw=true)
 </v>
@@ -2147,8 +2312,37 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Aligned Rectilinear"));</v>
       </c>
+      <c r="AN5" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_alignedrectilinear](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_alignedrectilinear.svg?raw=true)</v>
+      </c>
+      <c r="AO5" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Aligned Rectilinear](#aligned-rectilinear)</v>
+      </c>
+      <c r="AP5" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**</v>
+      </c>
+      <c r="AQ5" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AR5" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS5" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT5" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="6" spans="1:38" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -2174,13 +2368,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -2256,14 +2450,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Zig Zag](#zig-zag)</v>
       </c>
-      <c r="AH6" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH6" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI6" s="2" t="str">
+      <c r="AI6" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -2301,8 +2494,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Zig Zag"));</v>
       </c>
+      <c r="AN6" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_zigzag](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_zigzag.svg?raw=true)</v>
+      </c>
+      <c r="AO6" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Zig Zag](#zig-zag)</v>
+      </c>
+      <c r="AP6" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ6" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AR6" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS6" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT6" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="7" spans="1:38" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -2328,13 +2549,13 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N7">
         <v>4</v>
@@ -2410,14 +2631,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Cross Zag](#cross-zag)</v>
       </c>
-      <c r="AH7" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH7" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI7" s="2" t="str">
+      <c r="AI7" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -2455,8 +2675,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Cross Zag"));</v>
       </c>
+      <c r="AN7" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_crosszag](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_crosszag.svg?raw=true)</v>
+      </c>
+      <c r="AO7" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Cross Zag](#cross-zag)</v>
+      </c>
+      <c r="AP7" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ7" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AR7" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS7" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT7" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -2482,13 +2730,13 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -2564,14 +2812,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Locked Zag](#locked-zag)</v>
       </c>
-      <c r="AH8" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH8" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI8" s="2" t="str">
+      <c r="AI8" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -2609,8 +2856,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Locked Zag"));</v>
       </c>
+      <c r="AN8" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_lockedzag](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_lockedzag.svg?raw=true)</v>
+      </c>
+      <c r="AO8" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Locked Zag](#locked-zag)</v>
+      </c>
+      <c r="AP8" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ8" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AR8" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AS8" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AT8" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Extra-High</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -2636,10 +2911,10 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>56</v>
@@ -2718,14 +2993,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Line](#line)</v>
       </c>
-      <c r="AH9" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH9" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI9" s="2" t="str">
+      <c r="AI9" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -2763,13 +3037,41 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Line"));</v>
       </c>
+      <c r="AN9" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_line](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_line.svg?raw=true)</v>
+      </c>
+      <c r="AO9" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Line](#line)</v>
+      </c>
+      <c r="AP9" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ9" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR9" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS9" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT9" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -2787,13 +3089,13 @@
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>55</v>
@@ -2872,14 +3174,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Grid](#grid)</v>
       </c>
-      <c r="AH10" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH10" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI10" s="2" t="str">
+      <c r="AI10" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -2917,13 +3218,41 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Grid"));</v>
       </c>
+      <c r="AN10" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_grid](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_grid.svg?raw=true)</v>
+      </c>
+      <c r="AO10" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Grid](#grid)</v>
+      </c>
+      <c r="AP10" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ10" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR10" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AS10" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT10" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -2941,13 +3270,13 @@
         <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>58</v>
@@ -3026,14 +3355,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Triangles](#triangles)</v>
       </c>
-      <c r="AH11" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH11" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI11" s="2" t="str">
+      <c r="AI11" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3071,13 +3399,41 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Triangles"));</v>
       </c>
+      <c r="AN11" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_triangles](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_triangles.svg?raw=true)</v>
+      </c>
+      <c r="AO11" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Triangles](#triangles)</v>
+      </c>
+      <c r="AP11" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ11" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR11" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS11" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT11" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="12" spans="1:38" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -3095,13 +3451,13 @@
         <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>59</v>
@@ -3180,14 +3536,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Tri-hexagon](#tri-hexagon)</v>
       </c>
-      <c r="AH12" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH12" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI12" s="2" t="str">
+      <c r="AI12" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3225,8 +3580,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Tri-hexagon"));</v>
       </c>
+      <c r="AN12" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_tri-hexagon](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_tri-hexagon.svg?raw=true)</v>
+      </c>
+      <c r="AO12" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Tri-hexagon](#tri-hexagon)</v>
+      </c>
+      <c r="AP12" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ12" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR12" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AS12" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT12" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="E13">
         <v>11</v>
       </c>
@@ -3246,10 +3629,10 @@
         <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>57</v>
@@ -3328,14 +3711,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Cubic](#cubic)</v>
       </c>
-      <c r="AH13" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH13" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI13" s="2" t="str">
+      <c r="AI13" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3373,8 +3755,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Cubic"));</v>
       </c>
+      <c r="AN13" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_cubic](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_cubic.svg?raw=true)</v>
+      </c>
+      <c r="AO13" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Cubic](#cubic)</v>
+      </c>
+      <c r="AP13" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ13" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR13" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AS13" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT13" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="E14">
         <v>12</v>
       </c>
@@ -3394,10 +3804,10 @@
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>61</v>
@@ -3476,14 +3886,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Adaptive Cubic](#adaptive-cubic)</v>
       </c>
-      <c r="AH14" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH14" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI14" s="2" t="str">
+      <c r="AI14" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3521,8 +3930,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Adaptive Cubic"));</v>
       </c>
+      <c r="AN14" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_adaptivecubic](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_adaptivecubic.svg?raw=true)</v>
+      </c>
+      <c r="AO14" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Adaptive Cubic](#adaptive-cubic)</v>
+      </c>
+      <c r="AP14" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ14" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AR14" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AS14" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT14" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Low</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="E15">
         <v>13</v>
       </c>
@@ -3542,10 +3979,10 @@
         <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>66</v>
@@ -3624,14 +4061,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Quarter Cubic](#quarter-cubic)</v>
       </c>
-      <c r="AH15" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH15" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI15" s="2" t="str">
+      <c r="AI15" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3669,8 +4105,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Quarter Cubic"));</v>
       </c>
+      <c r="AN15" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_quartercubic](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_quartercubic.svg?raw=true)</v>
+      </c>
+      <c r="AO15" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Quarter Cubic](#quarter-cubic)</v>
+      </c>
+      <c r="AP15" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ15" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR15" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AS15" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT15" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" ht="120" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -3696,13 +4160,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>64</v>
@@ -3781,14 +4245,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Support Cubic](#support-cubic)</v>
       </c>
-      <c r="AH16" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH16" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI16" s="2" t="str">
+      <c r="AI16" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3826,8 +4289,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Support Cubic"));</v>
       </c>
+      <c r="AN16" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_supportcubic](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_supportcubic.svg?raw=true)</v>
+      </c>
+      <c r="AO16" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Support Cubic](#support-cubic)</v>
+      </c>
+      <c r="AP16" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ16" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR16" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS16" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AT16" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Extra-Low</v>
+      </c>
     </row>
-    <row r="17" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -3853,13 +4344,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>65</v>
@@ -3938,14 +4429,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Lightning](#lightning)</v>
       </c>
-      <c r="AH17" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH17" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI17" s="2" t="str">
+      <c r="AI17" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -3983,8 +4473,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Lightning"));</v>
       </c>
+      <c r="AN17" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_lightning](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_lightning.svg?raw=true)</v>
+      </c>
+      <c r="AO17" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Lightning](#lightning)</v>
+      </c>
+      <c r="AP17" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ17" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR17" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS17" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AT17" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Ultra-Low</v>
+      </c>
     </row>
-    <row r="18" spans="1:38" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1</v>
       </c>
@@ -4013,10 +4531,10 @@
         <v>9</v>
       </c>
       <c r="K18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>60</v>
@@ -4095,14 +4613,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Honeycomb](#honeycomb)</v>
       </c>
-      <c r="AH18" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH18" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI18" s="2" t="str">
+      <c r="AI18" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -4140,8 +4657,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Honeycomb"));</v>
       </c>
+      <c r="AN18" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_honeycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_honeycomb.svg?raw=true)</v>
+      </c>
+      <c r="AO18" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Honeycomb](#honeycomb)</v>
+      </c>
+      <c r="AP18" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ18" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR18" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AS18" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AT18" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Ultra-High</v>
+      </c>
     </row>
-    <row r="19" spans="1:38" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4170,13 +4715,13 @@
         <v>9</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -4252,14 +4797,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[3D Honeycomb](#3d-honeycomb)</v>
       </c>
-      <c r="AH19" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH19" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI19" s="2" t="str">
+      <c r="AI19" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -4297,8 +4841,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("3D Honeycomb"));</v>
       </c>
+      <c r="AN19" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_3dhoneycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_3dhoneycomb.svg?raw=true)</v>
+      </c>
+      <c r="AO19" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[3D Honeycomb](#3d-honeycomb)</v>
+      </c>
+      <c r="AP19" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ19" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AR19" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AS19" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AT19" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>High</v>
+      </c>
     </row>
-    <row r="20" spans="1:38" ht="165" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" ht="240" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -4321,19 +4893,19 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J20" t="s">
         <v>9</v>
       </c>
       <c r="K20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="N20">
         <v>3</v>
@@ -4409,14 +4981,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Lateral Honeycomb](#lateral-honeycomb)</v>
       </c>
-      <c r="AH20" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH20" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI20" s="2" t="str">
+      <c r="AI20" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -4430,7 +5001,7 @@
 ![infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;".png?raw=true)
 ","")</f>
         <v xml:space="preserve">## Lateral Honeycomb
-Vertical Honeycomb pattern. Acceptable torsional stiffness. Developed for low densities structures like wings. Improve over [2D Lattice](#2d-lattice) offers same performance with lower densities.This infill includes a Overhang angle parameter to improve the point of contact between layers and reduce the risk of delamination.
+Vertical Honeycomb pattern. Acceptable torsional stiffness. Developed for low densities structures like wings. Improve over [Lateral Lattice](#lateral-lattice) offers same performance with lower densities.This infill includes a Overhang angle parameter to improve the point of contact between layers and reduce the risk of delamination.
 - **Horizontal Strength (X-Y):** Normal-Low
 - **Vertical Strength (Z):** Normal-Low
 - **Density Calculation:**  % of  total infill volume
@@ -4454,8 +5025,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Lateral Honeycomb"));</v>
       </c>
+      <c r="AN20" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_lateral-honeycomb](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_lateral-honeycomb.svg?raw=true)</v>
+      </c>
+      <c r="AO20" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Lateral Honeycomb](#lateral-honeycomb)</v>
+      </c>
+      <c r="AP20" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ20" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AR20" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AS20" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT20" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="21" spans="1:38" ht="120" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4</v>
       </c>
@@ -4478,16 +5077,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
+        <v>188</v>
+      </c>
+      <c r="J21" t="s">
         <v>189</v>
       </c>
-      <c r="J21" t="s">
-        <v>190</v>
-      </c>
       <c r="K21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>89</v>
@@ -4566,14 +5165,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Lateral Lattice](#lateral-lattice)</v>
       </c>
-      <c r="AH21" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH21" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI21" s="2" t="str">
+      <c r="AI21" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -4611,8 +5209,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Lateral Lattice"));</v>
       </c>
+      <c r="AN21" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_lateral-lattice](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_lateral-lattice.svg?raw=true)</v>
+      </c>
+      <c r="AO21" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Lateral Lattice](#lateral-lattice)</v>
+      </c>
+      <c r="AP21" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ21" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AR21" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AS21" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT21" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="22" spans="1:38" ht="105" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" ht="240" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5</v>
       </c>
@@ -4638,16 +5264,16 @@
         <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -4723,14 +5349,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Cross Hatch](#cross-hatch)</v>
       </c>
-      <c r="AH22" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH22" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI22" s="2" t="str">
+      <c r="AI22" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -4769,8 +5394,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Cross Hatch"));</v>
       </c>
+      <c r="AN22" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_crosshatch](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_crosshatch.svg?raw=true)</v>
+      </c>
+      <c r="AO22" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Cross Hatch](#cross-hatch)</v>
+      </c>
+      <c r="AP22" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ22" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AR22" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AS22" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AT22" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-High</v>
+      </c>
     </row>
-    <row r="23" spans="1:38" ht="150" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:46" ht="225" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>6</v>
       </c>
@@ -4796,16 +5449,16 @@
         <v>8</v>
       </c>
       <c r="J23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -4881,14 +5534,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[TPMS-D](#tpms-d)</v>
       </c>
-      <c r="AH23" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH23" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI23" s="2" t="str">
+      <c r="AI23" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -4926,8 +5578,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("TPMS-D"));</v>
       </c>
+      <c r="AN23" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_tpmsd](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_tpmsd.svg?raw=true)</v>
+      </c>
+      <c r="AO23" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[TPMS-D](#tpms-d)</v>
+      </c>
+      <c r="AP23" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ23" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR23" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AS23" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AT23" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>High</v>
+      </c>
     </row>
-    <row r="24" spans="1:38" ht="180" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" ht="240" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7</v>
       </c>
@@ -4950,19 +5630,19 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K24" t="s">
+        <v>171</v>
+      </c>
+      <c r="L24" t="s">
         <v>172</v>
       </c>
-      <c r="L24" t="s">
-        <v>173</v>
-      </c>
       <c r="M24" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -5038,14 +5718,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[TPMS-FK](#tpms-fk)</v>
       </c>
-      <c r="AH24" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH24" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI24" s="2" t="str">
+      <c r="AI24" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5083,8 +5762,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("TPMS-FK"));</v>
       </c>
+      <c r="AN24" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_tpmsfk](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_tpmsfk.svg?raw=true)</v>
+      </c>
+      <c r="AO24" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[TPMS-FK](#tpms-fk)</v>
+      </c>
+      <c r="AP24" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ24" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AR24" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AS24" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AT24" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>High</v>
+      </c>
     </row>
-    <row r="25" spans="1:38" ht="210" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" ht="240" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>8</v>
       </c>
@@ -5110,13 +5817,13 @@
         <v>7</v>
       </c>
       <c r="J25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>90</v>
@@ -5195,14 +5902,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Gyroid](#gyroid)</v>
       </c>
-      <c r="AH25" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH25" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
       </c>
-      <c r="AI25" s="2" t="str">
+      <c r="AI25" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5240,8 +5946,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Gyroid"));</v>
       </c>
+      <c r="AN25" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_gyroid](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_gyroid.svg?raw=true)</v>
+      </c>
+      <c r="AO25" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Gyroid](#gyroid)</v>
+      </c>
+      <c r="AP25" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
+      </c>
+      <c r="AQ25" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AR25" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>High</v>
+      </c>
+      <c r="AS25" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AT25" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-High</v>
+      </c>
     </row>
-    <row r="26" spans="1:38" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" ht="270" x14ac:dyDescent="0.25">
       <c r="E26">
         <v>24</v>
       </c>
@@ -5258,13 +5992,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>54</v>
@@ -5343,17 +6077,15 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Concentric](#concentric)</v>
       </c>
-      <c r="AH26" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH26" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**</v>
       </c>
-      <c r="AI26" s="2" t="str">
+      <c r="AI26" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5375,8 +6107,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**
 ![infill-top-concentric](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-concentric.png?raw=true)
@@ -5394,8 +6125,38 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Concentric"));</v>
       </c>
+      <c r="AN26" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_concentric](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_concentric.svg?raw=true)</v>
+      </c>
+      <c r="AO26" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Concentric](#concentric)</v>
+      </c>
+      <c r="AP26" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**
+  - **[Ironing](quality_settings_ironing)**</v>
+      </c>
+      <c r="AQ26" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR26" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS26" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT26" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="27" spans="1:38" ht="180" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" ht="270" x14ac:dyDescent="0.25">
       <c r="E27">
         <v>25</v>
       </c>
@@ -5412,13 +6173,13 @@
         <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>73</v>
@@ -5497,16 +6258,14 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Hilbert Curve](#hilbert-curve)</v>
       </c>
-      <c r="AH27" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH27" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
-      <c r="AI27" s="2" t="str">
+      <c r="AI27" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5529,8 +6288,7 @@
 - **Print Time:** High
 - **Material/Time (Higher better):** Low
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-hilbert-curve](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-hilbert-curve.png?raw=true)
 </v>
@@ -5547,8 +6305,37 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Hilbert Curve"));</v>
       </c>
+      <c r="AN27" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_hilbertcurve](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_hilbertcurve.svg?raw=true)</v>
+      </c>
+      <c r="AO27" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Hilbert Curve](#hilbert-curve)</v>
+      </c>
+      <c r="AP27" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**</v>
+      </c>
+      <c r="AQ27" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR27" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS27" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AT27" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>High</v>
+      </c>
     </row>
-    <row r="28" spans="1:38" ht="120" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" ht="255" x14ac:dyDescent="0.25">
       <c r="E28">
         <v>26</v>
       </c>
@@ -5565,13 +6352,13 @@
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>63</v>
@@ -5650,16 +6437,14 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Archimedean Chords](#archimedean-chords)</v>
       </c>
-      <c r="AH28" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH28" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
-      <c r="AI28" s="2" t="str">
+      <c r="AI28" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5681,8 +6466,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-archimedean-chords](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-archimedean-chords.png?raw=true)
 </v>
@@ -5699,8 +6483,37 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Archimedean Chords"));</v>
       </c>
+      <c r="AN28" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_archimedeanchords](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_archimedeanchords.svg?raw=true)</v>
+      </c>
+      <c r="AO28" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Archimedean Chords](#archimedean-chords)</v>
+      </c>
+      <c r="AP28" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**</v>
+      </c>
+      <c r="AQ28" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR28" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS28" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-High</v>
+      </c>
+      <c r="AT28" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal-Low</v>
+      </c>
     </row>
-    <row r="29" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" ht="255" x14ac:dyDescent="0.25">
       <c r="E29">
         <v>27</v>
       </c>
@@ -5717,13 +6530,13 @@
         <v>15</v>
       </c>
       <c r="J29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>72</v>
@@ -5802,16 +6615,14 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[Octagram Spiral](#octagram-spiral)</v>
       </c>
-      <c r="AH29" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH29" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
-      <c r="AI29" s="2" t="str">
+      <c r="AI29" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5833,8 +6644,7 @@
 - **Print Time:** Normal
 - **Material/Time (Higher better):** Normal-Low
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-octagram-spiral](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-octagram-spiral.png?raw=true)
 </v>
@@ -5851,8 +6661,37 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v>def-&gt;enum_labels.push_back(L("Octagram Spiral"));</v>
       </c>
+      <c r="AN29" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![param_octagramspiral](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/param_octagramspiral.svg?raw=true)</v>
+      </c>
+      <c r="AO29" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[Octagram Spiral](#octagram-spiral)</v>
+      </c>
+      <c r="AP29" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Surface](strength_settings_top_bottom_shells)**</v>
+      </c>
+      <c r="AQ29" t="str">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>Low</v>
+      </c>
+      <c r="AR29" t="str">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>Normal</v>
+      </c>
+      <c r="AS29" s="1" t="str">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>Normal-Low</v>
+      </c>
+      <c r="AT29" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Normal</v>
+      </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="E30">
         <v>28</v>
       </c>
@@ -5866,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M30" s="8"/>
       <c r="O30" t="e">
@@ -5922,14 +6761,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[](#)</v>
       </c>
-      <c r="AH30" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH30" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v/>
       </c>
-      <c r="AI30" s="2" t="str">
+      <c r="AI30" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -5956,8 +6794,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v/>
       </c>
+      <c r="AN30" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/.svg?raw=true)</v>
+      </c>
+      <c r="AO30" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[](#)</v>
+      </c>
+      <c r="AP30" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v/>
+      </c>
+      <c r="AQ30" t="e">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AR30" t="e">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AS30" s="1" t="e">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AT30" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Ultra-Low</v>
+      </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="E31">
         <v>29</v>
       </c>
@@ -5971,7 +6837,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M31" s="8"/>
       <c r="O31" t="e">
@@ -6027,14 +6893,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[](#)</v>
       </c>
-      <c r="AH31" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH31" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v/>
       </c>
-      <c r="AI31" s="2" t="str">
+      <c r="AI31" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -6061,8 +6926,36 @@
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v/>
       </c>
+      <c r="AN31" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/.svg?raw=true)</v>
+      </c>
+      <c r="AO31" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[](#)</v>
+      </c>
+      <c r="AP31" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v/>
+      </c>
+      <c r="AQ31" t="e">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AR31" t="e">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AS31" s="1" t="e">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AT31" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Ultra-Low</v>
+      </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="E32">
         <v>30</v>
       </c>
@@ -6076,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M32" s="8"/>
       <c r="O32" t="e">
@@ -6132,14 +7025,13 @@
         <f>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</f>
         <v>[](#)</v>
       </c>
-      <c r="AH32" s="5" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <c r="AH32" s="10" t="str">
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v/>
       </c>
-      <c r="AI32" s="2" t="str">
+      <c r="AI32" s="8" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -6165,6 +7057,34 @@
       <c r="AL32" t="str">
         <f>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</f>
         <v/>
+      </c>
+      <c r="AN32" t="str">
+        <f>Infill[[#This Row],[SVG Link]]</f>
+        <v>![](https://github.com/SoftFever/OrcaSlicer/blob/main/resources/images/.svg?raw=true)</v>
+      </c>
+      <c r="AO32" s="1" t="str">
+        <f>Infill[[#This Row],[Pattern]]</f>
+        <v>[](#)</v>
+      </c>
+      <c r="AP32" t="str">
+        <f>Infill[[#This Row],[Applies to]]</f>
+        <v/>
+      </c>
+      <c r="AQ32" t="e">
+        <f>Infill[[#This Row],[X-Y Strength]]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AR32" t="e">
+        <f>Infill[[#This Row],[Z Strength]]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AS32" s="1" t="e">
+        <f>Infill[[#This Row],[Material/Time]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AT32" s="1" t="str">
+        <f>Infill[[#This Row],[Print Time]]</f>
+        <v>Ultra-Low</v>
       </c>
     </row>
   </sheetData>
@@ -6219,10 +7139,11 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="3">
+  <tableParts count="4">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/doc/print_settings/strength/infill_desc_calculator.xlsx
+++ b/doc/print_settings/strength/infill_desc_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Repos\OrcaSlicer\doc\print_settings\strength\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F288D4-B9A1-47D5-A3F9-DAAC4F36020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D9342C-2BC8-4E65-A1F6-5FE50430102E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{F7BCEEB8-8D62-4686-9FA1-C052039D2FF8}"/>
   </bookViews>
@@ -703,10 +703,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
@@ -737,6 +733,10 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1019,11 +1019,11 @@
       <calculatedColumnFormula>"["&amp;Infill[[#This Row],[name]]&amp;"](#"&amp;Infill[[#This Row],[nameMD]]&amp;")"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="31" xr3:uid="{D12C345A-0415-4208-969C-FE76BD14B76A}" name="Applies to" dataDxfId="0" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+      <calculatedColumnFormula>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{AE92B56B-1C4F-4A43-BC18-AFFF1480255E}" name="MD" dataDxfId="1" dataCellStyle="Porcentaje">
+    <tableColumn id="14" xr3:uid="{AE92B56B-1C4F-4A43-BC18-AFFF1480255E}" name="MD" dataDxfId="12" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]],Infill[[#This Row],[Is Ironing]]),"## "&amp;Infill[[#This Row],[name]]&amp;"
 "&amp;Infill[[#This Row],[Desc]]&amp;"
 - **Horizontal Strength (X-Y):** "&amp;Infill[[#This Row],[X-Y Strength]]&amp;"
@@ -1037,13 +1037,13 @@
 ![infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;"](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-"&amp;Infill[[#This Row],[nameMD]]&amp;".png?raw=true)
 ","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{B5B3DE03-E8E0-4448-BA81-E5B849AC0415}" name="s_keys_map" dataDxfId="12" dataCellStyle="Porcentaje">
+    <tableColumn id="26" xr3:uid="{B5B3DE03-E8E0-4448-BA81-E5B849AC0415}" name="s_keys_map" dataDxfId="11" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]])," { """&amp;Infill[[#This Row],[infill]]&amp;""", "&amp;Infill[[#This Row],[ip]]&amp;" },","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{DF1D46A6-663C-4993-9678-9483ECBDC09A}" name="Enum Pattern" dataDxfId="11" dataCellStyle="Porcentaje">
+    <tableColumn id="30" xr3:uid="{DF1D46A6-663C-4993-9678-9483ECBDC09A}" name="Enum Pattern" dataDxfId="10" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_values.push_back("""&amp;Infill[[#This Row],[infill]]&amp;""");","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{A375012B-C9F3-4FDF-8EA3-593D97EDEB2B}" name="Enum Pattern Names" dataDxfId="10" dataCellStyle="Porcentaje">
+    <tableColumn id="29" xr3:uid="{A375012B-C9F3-4FDF-8EA3-593D97EDEB2B}" name="Enum Pattern Names" dataDxfId="9" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(OR(Infill[[#This Row],[Is Infill]],Infill[[#This Row],[Is Surface]]),"def-&gt;enum_labels.push_back(L("""&amp;Infill[[#This Row],[name]]&amp;"""));","")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1067,7 +1067,7 @@
   <autoFilter ref="A16:C25" xr:uid="{8371D3BF-96D7-48EB-82A0-8021F9AA952E}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1D00CA6A-CEDD-45A1-8BA8-6DB7769D516C}" name="N"/>
-    <tableColumn id="2" xr3:uid="{3AC9B406-037B-4FD3-80D6-86F4D94EDB36}" name="Max %" dataDxfId="9" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{3AC9B406-037B-4FD3-80D6-86F4D94EDB36}" name="Max %" dataDxfId="8" dataCellStyle="Porcentaje"/>
     <tableColumn id="3" xr3:uid="{18E14714-6899-4575-90B8-4F97863AF141}" name="Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1078,25 +1078,25 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F85400E8-93F1-42C5-93F9-13851BAE5398}" name="Tabla4" displayName="Tabla4" ref="AN1:AT32" totalsRowShown="0">
   <autoFilter ref="AN1:AT32" xr:uid="{F85400E8-93F1-42C5-93F9-13851BAE5398}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{184C8A2D-5FE4-4972-8525-02DD0ED763F3}" name="-" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{184C8A2D-5FE4-4972-8525-02DD0ED763F3}" name="-" dataDxfId="7">
       <calculatedColumnFormula>Infill[[#This Row],[SVG Link]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{14A2CB57-4B88-4948-ABB5-B4E1F3AB50EF}" name="Pattern" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{14A2CB57-4B88-4948-ABB5-B4E1F3AB50EF}" name="Pattern" dataDxfId="6">
       <calculatedColumnFormula>Infill[[#This Row],[Pattern]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7FB40202-1341-4B88-81D2-89C268F45D4D}" name="Applies to" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{7FB40202-1341-4B88-81D2-89C268F45D4D}" name="Applies to" dataDxfId="5">
       <calculatedColumnFormula>Infill[[#This Row],[Applies to]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F83791FA-52BD-4574-8359-2DC84F1575E3}" name="X-Y Strength" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{F83791FA-52BD-4574-8359-2DC84F1575E3}" name="X-Y Strength" dataDxfId="4">
       <calculatedColumnFormula>Infill[[#This Row],[X-Y Strength]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A30810A1-1E95-4BAA-97B8-93C571CB8CF0}" name="Z Strength" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{A30810A1-1E95-4BAA-97B8-93C571CB8CF0}" name="Z Strength" dataDxfId="3">
       <calculatedColumnFormula>Infill[[#This Row],[Z Strength]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{630ACA64-21F3-4422-B317-D820E5C1F820}" name="Material Usage" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{630ACA64-21F3-4422-B317-D820E5C1F820}" name="Material Usage" dataDxfId="2">
       <calculatedColumnFormula>Infill[[#This Row],[Material/Time]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5F0A6FFD-7381-42EE-8794-FC0492BBA85C}" name="Print Time" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{5F0A6FFD-7381-42EE-8794-FC0492BBA85C}" name="Print Time" dataDxfId="1">
       <calculatedColumnFormula>Infill[[#This Row],[Print Time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1711,10 +1711,10 @@
         <v>[Monotonic](#monotonic)</v>
       </c>
       <c r="AH2" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AI2" s="8" t="str">
@@ -1739,7 +1739,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-monotonic](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-monotonic.png?raw=true)
 </v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AP2" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AQ2" t="str">
@@ -1895,10 +1895,10 @@
         <v>[Monotonic line](#monotonic-line)</v>
       </c>
       <c r="AH3" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AI3" s="8" t="str">
@@ -1923,7 +1923,7 @@
 - **Print Time:** Normal
 - **Material/Time (Higher better):** Normal
 - **Applies to:**
-  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-monotonic-line](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-monotonic-line.png?raw=true)
 </v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AP3" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AQ3" t="str">
@@ -2079,10 +2079,10 @@
         <v>[Rectilinear](#rectilinear)</v>
       </c>
       <c r="AH4" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**</v>
       </c>
@@ -2108,7 +2108,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**
 ![infill-top-rectilinear](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-rectilinear.png?raw=true)
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AP4" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**</v>
       </c>
@@ -2266,10 +2266,10 @@
         <v>[Aligned Rectilinear](#aligned-rectilinear)</v>
       </c>
       <c r="AH5" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AI5" s="8" t="str">
@@ -2295,7 +2295,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-aligned-rectilinear](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-aligned-rectilinear.png?raw=true)
 </v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AP5" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AQ5" t="str">
@@ -2451,7 +2451,7 @@
         <v>[Zig Zag](#zig-zag)</v>
       </c>
       <c r="AH6" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -2632,7 +2632,7 @@
         <v>[Cross Zag](#cross-zag)</v>
       </c>
       <c r="AH7" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -2813,7 +2813,7 @@
         <v>[Locked Zag](#locked-zag)</v>
       </c>
       <c r="AH8" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -2994,7 +2994,7 @@
         <v>[Line](#line)</v>
       </c>
       <c r="AH9" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -3175,7 +3175,7 @@
         <v>[Grid](#grid)</v>
       </c>
       <c r="AH10" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -3356,7 +3356,7 @@
         <v>[Triangles](#triangles)</v>
       </c>
       <c r="AH11" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -3537,7 +3537,7 @@
         <v>[Tri-hexagon](#tri-hexagon)</v>
       </c>
       <c r="AH12" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -3712,7 +3712,7 @@
         <v>[Cubic](#cubic)</v>
       </c>
       <c r="AH13" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -3887,7 +3887,7 @@
         <v>[Adaptive Cubic](#adaptive-cubic)</v>
       </c>
       <c r="AH14" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -4062,7 +4062,7 @@
         <v>[Quarter Cubic](#quarter-cubic)</v>
       </c>
       <c r="AH15" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -4246,7 +4246,7 @@
         <v>[Support Cubic](#support-cubic)</v>
       </c>
       <c r="AH16" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -4430,7 +4430,7 @@
         <v>[Lightning](#lightning)</v>
       </c>
       <c r="AH17" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -4614,7 +4614,7 @@
         <v>[Honeycomb](#honeycomb)</v>
       </c>
       <c r="AH18" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -4798,7 +4798,7 @@
         <v>[3D Honeycomb](#3d-honeycomb)</v>
       </c>
       <c r="AH19" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -4982,7 +4982,7 @@
         <v>[Lateral Honeycomb](#lateral-honeycomb)</v>
       </c>
       <c r="AH20" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -5166,7 +5166,7 @@
         <v>[Lateral Lattice](#lateral-lattice)</v>
       </c>
       <c r="AH21" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -5350,7 +5350,7 @@
         <v>[Cross Hatch](#cross-hatch)</v>
       </c>
       <c r="AH22" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -5535,7 +5535,7 @@
         <v>[TPMS-D](#tpms-d)</v>
       </c>
       <c r="AH23" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -5719,7 +5719,7 @@
         <v>[TPMS-FK](#tpms-fk)</v>
       </c>
       <c r="AH24" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -5903,7 +5903,7 @@
         <v>[Gyroid](#gyroid)</v>
       </c>
       <c r="AH25" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**</v>
@@ -5975,7 +5975,7 @@
         <v>Normal-High</v>
       </c>
     </row>
-    <row r="26" spans="1:46" ht="270" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" ht="255" x14ac:dyDescent="0.25">
       <c r="E26">
         <v>24</v>
       </c>
@@ -6078,10 +6078,10 @@
         <v>[Concentric](#concentric)</v>
       </c>
       <c r="AH26" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**</v>
       </c>
@@ -6107,7 +6107,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**
 ![infill-top-concentric](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-concentric.png?raw=true)
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AP26" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
   - **[Ironing](quality_settings_ironing)**</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>Normal-Low</v>
       </c>
     </row>
-    <row r="27" spans="1:46" ht="270" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" ht="255" x14ac:dyDescent="0.25">
       <c r="E27">
         <v>25</v>
       </c>
@@ -6259,10 +6259,10 @@
         <v>[Hilbert Curve](#hilbert-curve)</v>
       </c>
       <c r="AH27" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AI27" s="8" t="str">
@@ -6288,7 +6288,7 @@
 - **Print Time:** High
 - **Material/Time (Higher better):** Low
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-hilbert-curve](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-hilbert-curve.png?raw=true)
 </v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="AP27" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AQ27" t="str">
@@ -6335,7 +6335,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="28" spans="1:46" ht="255" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" ht="240" x14ac:dyDescent="0.25">
       <c r="E28">
         <v>26</v>
       </c>
@@ -6438,10 +6438,10 @@
         <v>[Archimedean Chords](#archimedean-chords)</v>
       </c>
       <c r="AH28" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AI28" s="8" t="str">
@@ -6466,7 +6466,7 @@
 - **Print Time:** Normal-Low
 - **Material/Time (Higher better):** Normal-High
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-archimedean-chords](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-archimedean-chords.png?raw=true)
 </v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="AP28" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AQ28" t="str">
@@ -6513,7 +6513,7 @@
         <v>Normal-Low</v>
       </c>
     </row>
-    <row r="29" spans="1:46" ht="255" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" ht="240" x14ac:dyDescent="0.25">
       <c r="E29">
         <v>27</v>
       </c>
@@ -6616,10 +6616,10 @@
         <v>[Octagram Spiral](#octagram-spiral)</v>
       </c>
       <c r="AH29" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AI29" s="8" t="str">
@@ -6644,7 +6644,7 @@
 - **Print Time:** Normal
 - **Material/Time (Higher better):** Normal-Low
 - **Applies to:**
-  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**
 ![infill-top-octagram-spiral](https://github.com/SoftFever/OrcaSlicer/blob/main/doc/images/fill/infill-top-octagram-spiral.png?raw=true)
 </v>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AP29" t="str">
         <f>Infill[[#This Row],[Applies to]]</f>
-        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**
+        <v xml:space="preserve">  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**
   - **[Surface](strength_settings_top_bottom_shells)**</v>
       </c>
       <c r="AQ29" t="str">
@@ -6762,7 +6762,7 @@
         <v>[](#)</v>
       </c>
       <c r="AH30" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v/>
@@ -6894,7 +6894,7 @@
         <v>[](#)</v>
       </c>
       <c r="AH31" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v/>
@@ -7026,7 +7026,7 @@
         <v>[](#)</v>
       </c>
       <c r="AH32" s="10" t="str">
-        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_top_bottom_shells#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
+        <f>IF(Infill[[#This Row],[Is Infill]],"  - **[Sparse Infill](strength_settings_infill#sparse-infill-density)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"  - **[Solid Infill](strength_settings_infill#internal-solid-infill)**",)&amp;IF(Infill[[#This Row],[Is Surface]],"
   - **[Surface](strength_settings_top_bottom_shells)**",)&amp;IF(Infill[[#This Row],[Is Ironing]],"
   - **[Ironing](quality_settings_ironing)**",)</f>
         <v/>
